--- a/output/HS_Code_Summary_4Leaders_LCL14.xlsx
+++ b/output/HS_Code_Summary_4Leaders_LCL14.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Poznamky a upozorneni" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Souhrn HS kodu'!$A$5:$P$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Polozky detail'!$A$1:$R$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Souhrn HS kodu'!$A$5:$M$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Polozky detail'!$A$1:$O$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -601,14 +601,11 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -675,40 +672,25 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Cena dle faktury (USD)</t>
+          <t>Cena / celni hodnota (USD)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Sleva (USD)</t>
+          <t>Incoterms</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Naklady LCL (USD)</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Celni hodnota (USD)</t>
+          <t>Antidumping</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>Incoterms</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>CBAM</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>Antidumping</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Polozky c.</t>
         </is>
@@ -731,10 +713,7 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="n"/>
       <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -772,33 +751,24 @@
         <v>2.5</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L7" s="11" t="n">
         <v>151.09</v>
       </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -840,33 +810,24 @@
         <v>126.4</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>737.6</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="L8" s="11" t="n">
         <v>742.97</v>
       </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>5, 26, 51</t>
         </is>
@@ -908,33 +869,24 @@
         <v>5</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="L9" s="11" t="n">
         <v>80.58</v>
       </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -976,33 +928,24 @@
         <v>117.3</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>558.6</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="L10" s="11" t="n">
         <v>562.66</v>
       </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O10" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>13, 30, 48</t>
         </is>
@@ -1044,33 +987,24 @@
         <v>132</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>292</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="L11" s="11" t="n">
         <v>294.12</v>
       </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O11" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -1112,33 +1046,24 @@
         <v>137.5</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>644.16</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="L12" s="11" t="n">
         <v>648.85</v>
       </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -1180,33 +1105,24 @@
         <v>497.2</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>1866.4</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>13.56</v>
-      </c>
-      <c r="L13" s="11" t="n">
         <v>1879.96</v>
       </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>14, 19, 32, 37, 39, 40</t>
         </is>
@@ -1248,33 +1164,24 @@
         <v>120.6</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>472.5</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="11" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="L14" s="11" t="n">
         <v>475.94</v>
       </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -1316,33 +1223,24 @@
         <v>51</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>624</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="L15" s="11" t="n">
         <v>628.54</v>
       </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -1384,33 +1282,24 @@
         <v>36.8</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>290</v>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="L16" s="11" t="n">
         <v>292.11</v>
       </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1452,33 +1341,24 @@
         <v>178.5</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>567</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="L17" s="11" t="n">
         <v>571.12</v>
       </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1520,33 +1400,24 @@
         <v>66</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>282</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="L18" s="11" t="n">
         <v>284.05</v>
       </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -1588,33 +1459,24 @@
         <v>236</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>1550</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="L19" s="11" t="n">
         <v>1561.27</v>
       </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1656,33 +1518,24 @@
         <v>1783.6</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>9506</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>69.14</v>
-      </c>
-      <c r="L20" s="11" t="n">
         <v>9575.139999999999</v>
       </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1724,33 +1577,24 @@
         <v>94</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1725</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="L21" s="11" t="n">
         <v>1737.55</v>
       </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1792,33 +1636,24 @@
         <v>110.5</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>884</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="11" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="L22" s="11" t="n">
         <v>890.4299999999999</v>
       </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1860,33 +1695,24 @@
         <v>6.8</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>130</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L23" s="11" t="n">
         <v>130.95</v>
       </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N23" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -1928,33 +1754,24 @@
         <v>307.5</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1293.6</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="11" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="L24" s="11" t="n">
         <v>1303.01</v>
       </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N24" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -1996,33 +1813,24 @@
         <v>156.1</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1025</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="11" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="L25" s="11" t="n">
         <v>1032.46</v>
       </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M25" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>15, 42</t>
         </is>
@@ -2064,33 +1872,24 @@
         <v>945</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>4305</v>
-      </c>
-      <c r="J26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="16" t="n">
-        <v>31.31</v>
-      </c>
-      <c r="L26" s="16" t="n">
         <v>4336.31</v>
       </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>ANO - hlinik, KN 7616 (priloha I nar. 2023/956)</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>OVERIT - ex 7616 99 90 spada do rozsahu AD opatreni na hlinikove vytlacovane vyrobky z CN (nar. (EU) 2021/546), pokud jde o extrudovany profil</t>
+        </is>
+      </c>
       <c r="M26" s="12" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N26" s="13" t="inlineStr">
-        <is>
-          <t>ANO - hlinik, KN 7616 (priloha I nar. 2023/956)</t>
-        </is>
-      </c>
-      <c r="O26" s="13" t="inlineStr">
-        <is>
-          <t>OVERIT - ex 7616 99 90 spada do rozsahu AD opatreni na hlinikove vytlacovane vyrobky z CN (nar. (EU) 2021/546), pokud jde o extrudovany profil</t>
-        </is>
-      </c>
-      <c r="P26" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2132,33 +1931,24 @@
         <v>48</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>208</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="L27" s="11" t="n">
         <v>209.51</v>
       </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -2200,33 +1990,24 @@
         <v>122.4</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>696</v>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="11" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="L28" s="11" t="n">
         <v>701.0599999999999</v>
       </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O28" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2268,33 +2049,24 @@
         <v>60</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>336</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="L29" s="11" t="n">
         <v>338.45</v>
       </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>6, 28</t>
         </is>
@@ -2336,33 +2108,24 @@
         <v>50.1</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>178.2</v>
-      </c>
-      <c r="J30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L30" s="11" t="n">
         <v>179.5</v>
       </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O30" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -2404,33 +2167,24 @@
         <v>18.5</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>125</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="11" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L31" s="11" t="n">
         <v>125.91</v>
       </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O31" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -2472,33 +2226,24 @@
         <v>71.5</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>612.5</v>
-      </c>
-      <c r="J32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="11" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="L32" s="11" t="n">
         <v>616.95</v>
       </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O32" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P32" s="7" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -2540,33 +2285,24 @@
         <v>64.8</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>652.5</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L33" s="11" t="n">
         <v>657.25</v>
       </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M33" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O33" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -2608,33 +2344,24 @@
         <v>134.4</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1036.8</v>
-      </c>
-      <c r="J34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="11" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="L34" s="11" t="n">
         <v>1044.34</v>
       </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M34" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O34" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P34" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2676,33 +2403,24 @@
         <v>251.9</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>817</v>
-      </c>
-      <c r="J35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="11" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="L35" s="11" t="n">
         <v>822.9400000000001</v>
       </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M35" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N35" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O35" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>11, 31</t>
         </is>
@@ -2744,33 +2462,24 @@
         <v>321</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>2507.6</v>
-      </c>
-      <c r="J36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="11" t="n">
-        <v>18.24</v>
-      </c>
-      <c r="L36" s="11" t="n">
         <v>2525.84</v>
       </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M36" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O36" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P36" s="7" t="inlineStr">
         <is>
           <t>21, 24, 36</t>
         </is>
@@ -2812,33 +2521,24 @@
         <v>46.5</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>734.4</v>
-      </c>
-      <c r="J37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="11" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="L37" s="11" t="n">
         <v>739.74</v>
       </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N37" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O37" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P37" s="7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -2880,33 +2580,24 @@
         <v>450</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>2490</v>
-      </c>
-      <c r="J38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="11" t="n">
-        <v>18.11</v>
-      </c>
-      <c r="L38" s="11" t="n">
         <v>2508.11</v>
       </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N38" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O38" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P38" s="7" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -2948,33 +2639,24 @@
         <v>154.4</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>790.5599999999999</v>
-      </c>
-      <c r="J39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L39" s="11" t="n">
         <v>796.3099999999999</v>
       </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O39" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P39" s="7" t="inlineStr">
         <is>
           <t>7, 23</t>
         </is>
@@ -3016,33 +2698,24 @@
         <v>20.5</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>164</v>
-      </c>
-      <c r="J40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="L40" s="11" t="n">
         <v>165.19</v>
       </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O40" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -3084,33 +2757,24 @@
         <v>140</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>576</v>
-      </c>
-      <c r="J41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="11" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="L41" s="11" t="n">
         <v>580.1900000000001</v>
       </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M41" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O41" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P41" s="7" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -3152,33 +2816,24 @@
         <v>123.9</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>735</v>
-      </c>
-      <c r="J42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="11" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="L42" s="11" t="n">
         <v>740.35</v>
       </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M42" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O42" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P42" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -3220,33 +2875,24 @@
         <v>31</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>230</v>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="L43" s="11" t="n">
         <v>231.67</v>
       </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M43" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O43" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P43" s="7" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -3278,26 +2924,13 @@
         <f>SUM(I7:I43)</f>
         <v/>
       </c>
-      <c r="J44" s="21">
-        <f>SUM(J7:J43)</f>
+      <c r="J44" s="18">
+        <f> Total na fakture: 40162.42 USD</f>
         <v/>
       </c>
-      <c r="K44" s="21">
-        <f>SUM(K7:K43)</f>
-        <v/>
-      </c>
-      <c r="L44" s="21">
-        <f>SUM(L7:L43)</f>
-        <v/>
-      </c>
-      <c r="M44" s="18" t="inlineStr">
-        <is>
-          <t>Fa celkem 40162.42 USD</t>
-        </is>
-      </c>
-      <c r="N44" s="17" t="n"/>
-      <c r="O44" s="17" t="n"/>
-      <c r="P44" s="17" t="n"/>
+      <c r="K44" s="17" t="n"/>
+      <c r="L44" s="17" t="n"/>
+      <c r="M44" s="17" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3316,10 +2949,7 @@
       <c r="J45" s="5" t="n"/>
       <c r="K45" s="5" t="n"/>
       <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="n"/>
-      <c r="O45" s="5" t="n"/>
-      <c r="P45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -3357,33 +2987,24 @@
         <v>403.2</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>1650.6</v>
-      </c>
-      <c r="J46" s="11" t="n">
-        <v>-119.83</v>
-      </c>
-      <c r="K46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="11" t="n">
         <v>1530.77</v>
       </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N46" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O46" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P46" s="7" t="inlineStr">
         <is>
           <t>54</t>
         </is>
@@ -3425,33 +3046,24 @@
         <v>510</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>1077.12</v>
-      </c>
-      <c r="J47" s="11" t="n">
-        <v>-78.2</v>
-      </c>
-      <c r="K47" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="11" t="n">
         <v>998.92</v>
       </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N47" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O47" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P47" s="7" t="inlineStr">
         <is>
           <t>59</t>
         </is>
@@ -3493,33 +3105,24 @@
         <v>324</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>1278</v>
-      </c>
-      <c r="J48" s="11" t="n">
-        <v>-92.78</v>
-      </c>
-      <c r="K48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="11" t="n">
         <v>1185.22</v>
       </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N48" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O48" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P48" s="7" t="inlineStr">
         <is>
           <t>56</t>
         </is>
@@ -3561,33 +3164,24 @@
         <v>618.5</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>2917.2</v>
-      </c>
-      <c r="J49" s="11" t="n">
-        <v>-211.79</v>
-      </c>
-      <c r="K49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="11" t="n">
         <v>2705.41</v>
       </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N49" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O49" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P49" s="7" t="inlineStr">
         <is>
           <t>53, 60</t>
         </is>
@@ -3629,33 +3223,24 @@
         <v>374</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>829.92</v>
-      </c>
-      <c r="J50" s="11" t="n">
-        <v>-60.25</v>
-      </c>
-      <c r="K50" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="11" t="n">
         <v>769.67</v>
       </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M50" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N50" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O50" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P50" s="7" t="inlineStr">
         <is>
           <t>57</t>
         </is>
@@ -3697,33 +3282,24 @@
         <v>264.6</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>3494.4</v>
-      </c>
-      <c r="J51" s="11" t="n">
-        <v>-253.7</v>
-      </c>
-      <c r="K51" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="11" t="n">
         <v>3240.7</v>
       </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N51" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O51" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P51" s="7" t="inlineStr">
         <is>
           <t>61</t>
         </is>
@@ -3765,33 +3341,24 @@
         <v>88</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>1298</v>
-      </c>
-      <c r="J52" s="11" t="n">
-        <v>-94.23999999999999</v>
-      </c>
-      <c r="K52" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="11" t="n">
         <v>1203.76</v>
       </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L52" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M52" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N52" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O52" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P52" s="7" t="inlineStr">
         <is>
           <t>62</t>
         </is>
@@ -3833,33 +3400,24 @@
         <v>88</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>574.5599999999999</v>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>-41.71</v>
-      </c>
-      <c r="K53" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="11" t="n">
         <v>532.85</v>
       </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N53" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O53" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P53" s="7" t="inlineStr">
         <is>
           <t>58</t>
         </is>
@@ -3901,33 +3459,24 @@
         <v>44</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>430.56</v>
-      </c>
-      <c r="J54" s="11" t="n">
-        <v>-31.26</v>
-      </c>
-      <c r="K54" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="11" t="n">
         <v>399.3</v>
       </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M54" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N54" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O54" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P54" s="7" t="inlineStr">
         <is>
           <t>55</t>
         </is>
@@ -3959,26 +3508,13 @@
         <f>SUM(I46:I54)</f>
         <v/>
       </c>
-      <c r="J55" s="21">
-        <f>SUM(J46:J54)</f>
+      <c r="J55" s="18">
+        <f> Total na fakture: 12566.60 USD</f>
         <v/>
       </c>
-      <c r="K55" s="21">
-        <f>SUM(K46:K54)</f>
-        <v/>
-      </c>
-      <c r="L55" s="21">
-        <f>SUM(L46:L54)</f>
-        <v/>
-      </c>
-      <c r="M55" s="18" t="inlineStr">
-        <is>
-          <t>Fa celkem 12566.60 USD</t>
-        </is>
-      </c>
-      <c r="N55" s="17" t="n"/>
-      <c r="O55" s="17" t="n"/>
-      <c r="P55" s="17" t="n"/>
+      <c r="K55" s="17" t="n"/>
+      <c r="L55" s="17" t="n"/>
+      <c r="M55" s="17" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -3997,10 +3533,7 @@
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="5" t="n"/>
       <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="n"/>
-      <c r="O56" s="5" t="n"/>
-      <c r="P56" s="6" t="n"/>
+      <c r="M56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -4038,33 +3571,24 @@
         <v>40</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>490</v>
-      </c>
-      <c r="J57" s="11" t="n">
-        <v>-54.13</v>
-      </c>
-      <c r="K57" s="11" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="L57" s="11" t="n">
         <v>450.71</v>
       </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N57" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O57" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P57" s="7" t="inlineStr">
         <is>
           <t>66, 67</t>
         </is>
@@ -4106,33 +3630,24 @@
         <v>150</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>417.6</v>
-      </c>
-      <c r="J58" s="11" t="n">
-        <v>-46.13</v>
-      </c>
-      <c r="K58" s="11" t="n">
-        <v>12.65</v>
-      </c>
-      <c r="L58" s="11" t="n">
         <v>384.12</v>
       </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M58" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N58" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O58" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P58" s="7" t="inlineStr">
         <is>
           <t>64</t>
         </is>
@@ -4174,33 +3689,24 @@
         <v>4.65</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>96</v>
-      </c>
-      <c r="J59" s="11" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="K59" s="11" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L59" s="11" t="n">
         <v>88.31</v>
       </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N59" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O59" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P59" s="7" t="inlineStr">
         <is>
           <t>71</t>
         </is>
@@ -4242,33 +3748,24 @@
         <v>169</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>1976</v>
-      </c>
-      <c r="J60" s="11" t="n">
-        <v>-218.28</v>
-      </c>
-      <c r="K60" s="11" t="n">
-        <v>59.86</v>
-      </c>
-      <c r="L60" s="11" t="n">
         <v>1817.58</v>
       </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N60" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O60" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P60" s="7" t="inlineStr">
         <is>
           <t>72</t>
         </is>
@@ -4310,33 +3807,24 @@
         <v>36</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>625</v>
-      </c>
-      <c r="J61" s="11" t="n">
-        <v>-69.04000000000001</v>
-      </c>
-      <c r="K61" s="11" t="n">
-        <v>18.93</v>
-      </c>
-      <c r="L61" s="11" t="n">
         <v>574.89</v>
       </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N61" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O61" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P61" s="7" t="inlineStr">
         <is>
           <t>68</t>
         </is>
@@ -4378,33 +3866,24 @@
         <v>19.15</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>231</v>
-      </c>
-      <c r="J62" s="11" t="n">
-        <v>-25.52</v>
-      </c>
-      <c r="K62" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="L62" s="11" t="n">
         <v>212.48</v>
       </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M62" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N62" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O62" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P62" s="7" t="inlineStr">
         <is>
           <t>65</t>
         </is>
@@ -4446,33 +3925,24 @@
         <v>420</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>2205</v>
-      </c>
-      <c r="J63" s="11" t="n">
-        <v>-243.57</v>
-      </c>
-      <c r="K63" s="11" t="n">
-        <v>66.78</v>
-      </c>
-      <c r="L63" s="11" t="n">
         <v>2028.21</v>
       </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M63" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N63" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O63" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P63" s="7" t="inlineStr">
         <is>
           <t>69</t>
         </is>
@@ -4514,33 +3984,24 @@
         <v>30</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>304</v>
-      </c>
-      <c r="J64" s="11" t="n">
-        <v>-33.58</v>
-      </c>
-      <c r="K64" s="11" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="L64" s="11" t="n">
         <v>279.63</v>
       </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M64" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N64" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O64" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P64" s="7" t="inlineStr">
         <is>
           <t>63</t>
         </is>
@@ -4582,33 +4043,24 @@
         <v>55.8</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>258</v>
-      </c>
-      <c r="J65" s="11" t="n">
-        <v>-28.5</v>
-      </c>
-      <c r="K65" s="11" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="L65" s="11" t="n">
         <v>237.32</v>
       </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>FOB Ningbo</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
       <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>FOB Ningbo</t>
-        </is>
-      </c>
-      <c r="N65" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="O65" s="8" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="P65" s="7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -4640,26 +4092,13 @@
         <f>SUM(I57:I65)</f>
         <v/>
       </c>
-      <c r="J66" s="21">
-        <f>SUM(J57:J65)</f>
+      <c r="J66" s="18">
+        <f> Total na fakture: 6073.25 USD</f>
         <v/>
       </c>
-      <c r="K66" s="21">
-        <f>SUM(K57:K65)</f>
-        <v/>
-      </c>
-      <c r="L66" s="21">
-        <f>SUM(L57:L65)</f>
-        <v/>
-      </c>
-      <c r="M66" s="18" t="inlineStr">
-        <is>
-          <t>Fa celkem 6073.25 USD</t>
-        </is>
-      </c>
-      <c r="N66" s="17" t="n"/>
-      <c r="O66" s="17" t="n"/>
-      <c r="P66" s="17" t="n"/>
+      <c r="K66" s="17" t="n"/>
+      <c r="L66" s="17" t="n"/>
+      <c r="M66" s="17" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="17" t="n"/>
@@ -4681,67 +4120,58 @@
         <v>10858.1</v>
       </c>
       <c r="I68" s="25" t="n">
-        <v>60025.38</v>
-      </c>
-      <c r="J68" s="25" t="n">
-        <v>-1713.11</v>
-      </c>
-      <c r="K68" s="25" t="n">
-        <v>490</v>
-      </c>
-      <c r="L68" s="25" t="n">
         <v>58802.27</v>
       </c>
+      <c r="J68" s="17" t="n"/>
+      <c r="K68" s="17" t="n"/>
+      <c r="L68" s="17" t="n"/>
       <c r="M68" s="17" t="n"/>
-      <c r="N68" s="17" t="n"/>
-      <c r="O68" s="17" t="n"/>
-      <c r="P68" s="17" t="n"/>
     </row>
     <row r="70">
       <c r="D70" s="26" t="inlineStr">
         <is>
-          <t>KONTROLA PROTI FAKTURAM</t>
+          <t>KONTROLA PROTI FAKTURAM - castka uvedena u "Total"</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ningbo Onway Imp &amp; Exp Co., Ltd. - fa 26OW08001 LCL14, celkem dle faktury</t>
-        </is>
-      </c>
-      <c r="L71" s="27" t="n">
+          <t>Ningbo Onway Imp &amp; Exp Co., Ltd. - fa 26OW08001 LCL14, castka u "Total"</t>
+        </is>
+      </c>
+      <c r="I71" s="27" t="n">
         <v>40162.42</v>
       </c>
     </row>
     <row r="72">
       <c r="D72" t="inlineStr">
         <is>
-          <t>Hefei Howell E-commerce Co., Ltd. - fa 4L26016S/1 (LCL14/1), celkem dle faktury</t>
-        </is>
-      </c>
-      <c r="L72" s="27" t="n">
+          <t>Hefei Howell E-commerce Co., Ltd. - fa 4L26016S/1 (LCL14/1), castka u "Total"</t>
+        </is>
+      </c>
+      <c r="I72" s="27" t="n">
         <v>12566.6</v>
       </c>
     </row>
     <row r="73">
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ningbo HowellGoods Import and Export Co., Ltd. - fa 4L26016S/2 (LCL14/2), celkem dle faktury</t>
-        </is>
-      </c>
-      <c r="L73" s="27" t="n">
+          <t>Ningbo HowellGoods Import and Export Co., Ltd. - fa 4L26016S/2 (LCL14/2), castka u "Total"</t>
+        </is>
+      </c>
+      <c r="I73" s="27" t="n">
         <v>6073.25</v>
       </c>
     </row>
     <row r="74">
       <c r="D74" s="26" t="inlineStr">
         <is>
-          <t>Soucet fakturovanych castek (musi se rovnat celni hodnote vyse)</t>
-        </is>
-      </c>
-      <c r="L74" s="28">
-        <f>SUM(L71:L73)</f>
+          <t>Soucet castek u "Total" na fakturach (musi se rovnat souctu vyse)</t>
+        </is>
+      </c>
+      <c r="I74" s="28">
+        <f>SUM(I71:I73)</f>
         <v/>
       </c>
     </row>
@@ -4751,20 +4181,20 @@
           <t>Rozdil (musi byt 0,00)</t>
         </is>
       </c>
-      <c r="L75" s="28">
-        <f>L68-L74</f>
+      <c r="I75" s="28">
+        <f>I68-I74</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:P67"/>
+  <autoFilter ref="A5:M67"/>
   <mergeCells count="6">
-    <mergeCell ref="A45:P45"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A56:P56"/>
-    <mergeCell ref="A6:P6"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A56:M56"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4776,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4791,12 +4221,9 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
-    <col width="58" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="58" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -4862,30 +4289,15 @@
       </c>
       <c r="M1" s="3" t="inlineStr">
         <is>
-          <t>Jedn. cena (USD)</t>
+          <t>Jedn. cena dle faktury (USD)</t>
         </is>
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>Cena dle faktury (USD)</t>
+          <t>Cena / celni hodnota (USD)</t>
         </is>
       </c>
       <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Sleva (USD)</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Naklady LCL (USD)</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Celni hodnota (USD)</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Poznamka</t>
         </is>
@@ -4946,18 +4358,9 @@
         <v>4.85</v>
       </c>
       <c r="N2" s="16" t="n">
-        <v>9506</v>
-      </c>
-      <c r="O2" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="16" t="n">
-        <v>69.14</v>
-      </c>
-      <c r="Q2" s="16" t="n">
         <v>9575.139999999999</v>
       </c>
-      <c r="R2" s="13" t="inlineStr">
+      <c r="O2" s="13" t="inlineStr">
         <is>
           <t>HS kod opraven z 6104 43 00 00 na 6110 30 99 00 - Oprava dle e-mailu P. Vojtechove 18/09/2026 - spatne zarazeni zjisteno pri kontrole kontejneru</t>
         </is>
@@ -5018,18 +4421,9 @@
         <v>1.55</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>1550</v>
-      </c>
-      <c r="O3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="11" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="Q3" s="11" t="n">
         <v>1561.27</v>
       </c>
-      <c r="R3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -5086,18 +4480,9 @@
         <v>0.52</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>884</v>
-      </c>
-      <c r="O4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="11" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="Q4" s="11" t="n">
         <v>890.4299999999999</v>
       </c>
-      <c r="R4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -5154,18 +4539,9 @@
         <v>6.15</v>
       </c>
       <c r="N5" s="16" t="n">
-        <v>4305</v>
-      </c>
-      <c r="O5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="16" t="n">
-        <v>31.31</v>
-      </c>
-      <c r="Q5" s="16" t="n">
         <v>4336.31</v>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>CBAM: ANO - hlinik, KN 7616 (priloha I nar. 2023/956)</t>
         </is>
@@ -5226,18 +4602,9 @@
         <v>0.68</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>285.6</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q6" s="11" t="n">
         <v>287.68</v>
       </c>
-      <c r="R6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -5294,18 +4661,9 @@
         <v>0.7</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>140</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Q7" s="11" t="n">
         <v>141.02</v>
       </c>
-      <c r="R7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -5362,18 +4720,9 @@
         <v>1.88</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>473.76</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q8" s="11" t="n">
         <v>477.21</v>
       </c>
-      <c r="R8" s="8" t="inlineStr"/>
+      <c r="O8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -5430,18 +4779,9 @@
         <v>1.08</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>1036.8</v>
-      </c>
-      <c r="O9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="11" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="Q9" s="11" t="n">
         <v>1044.34</v>
       </c>
-      <c r="R9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -5498,18 +4838,9 @@
         <v>1.38</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>1725</v>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="11" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="Q10" s="11" t="n">
         <v>1737.55</v>
       </c>
-      <c r="R10" s="8" t="inlineStr"/>
+      <c r="O10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -5566,18 +4897,9 @@
         <v>0.87</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>696</v>
-      </c>
-      <c r="O11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="11" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="Q11" s="11" t="n">
         <v>701.0599999999999</v>
       </c>
-      <c r="R11" s="8" t="inlineStr"/>
+      <c r="O11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5634,18 +4956,9 @@
         <v>4.65</v>
       </c>
       <c r="N12" s="11" t="n">
-        <v>465</v>
-      </c>
-      <c r="O12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="11" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="Q12" s="11" t="n">
         <v>468.38</v>
       </c>
-      <c r="R12" s="8" t="inlineStr"/>
+      <c r="O12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -5702,18 +5015,9 @@
         <v>1.75</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>735</v>
-      </c>
-      <c r="O13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="11" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="Q13" s="11" t="n">
         <v>740.35</v>
       </c>
-      <c r="R13" s="8" t="inlineStr"/>
+      <c r="O13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -5770,18 +5074,9 @@
         <v>0.38</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>159.6</v>
-      </c>
-      <c r="O14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Q14" s="11" t="n">
         <v>160.76</v>
       </c>
-      <c r="R14" s="8" t="inlineStr"/>
+      <c r="O14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -5838,18 +5133,9 @@
         <v>0.73</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>365</v>
-      </c>
-      <c r="O15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q15" s="11" t="n">
         <v>367.65</v>
       </c>
-      <c r="R15" s="8" t="inlineStr"/>
+      <c r="O15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -5906,18 +5192,9 @@
         <v>0.58</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>870</v>
-      </c>
-      <c r="O16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="11" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="Q16" s="11" t="n">
         <v>876.33</v>
       </c>
-      <c r="R16" s="8" t="inlineStr"/>
+      <c r="O16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -5974,18 +5251,9 @@
         <v>1.45</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>290</v>
-      </c>
-      <c r="O17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q17" s="11" t="n">
         <v>292.11</v>
       </c>
-      <c r="R17" s="8" t="inlineStr"/>
+      <c r="O17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -6042,18 +5310,9 @@
         <v>1.75</v>
       </c>
       <c r="N18" s="11" t="n">
-        <v>472.5</v>
-      </c>
-      <c r="O18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="11" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q18" s="11" t="n">
         <v>475.94</v>
       </c>
-      <c r="R18" s="8" t="inlineStr"/>
+      <c r="O18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -6110,18 +5369,9 @@
         <v>7.25</v>
       </c>
       <c r="N19" s="11" t="n">
-        <v>652.5</v>
-      </c>
-      <c r="O19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Q19" s="11" t="n">
         <v>657.25</v>
       </c>
-      <c r="R19" s="8" t="inlineStr"/>
+      <c r="O19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -6178,18 +5428,9 @@
         <v>2.3</v>
       </c>
       <c r="N20" s="11" t="n">
-        <v>558.9</v>
-      </c>
-      <c r="O20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="11" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="Q20" s="11" t="n">
         <v>562.96</v>
       </c>
-      <c r="R20" s="8" t="inlineStr"/>
+      <c r="O20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -6246,18 +5487,9 @@
         <v>10.2</v>
       </c>
       <c r="N21" s="11" t="n">
-        <v>734.4</v>
-      </c>
-      <c r="O21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="11" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="Q21" s="11" t="n">
         <v>739.74</v>
       </c>
-      <c r="R21" s="8" t="inlineStr"/>
+      <c r="O21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -6314,18 +5546,9 @@
         <v>2.9</v>
       </c>
       <c r="N22" s="11" t="n">
-        <v>974.4</v>
-      </c>
-      <c r="O22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="11" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="Q22" s="11" t="n">
         <v>981.49</v>
       </c>
-      <c r="R22" s="8" t="inlineStr"/>
+      <c r="O22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -6382,18 +5605,9 @@
         <v>1.83</v>
       </c>
       <c r="N23" s="11" t="n">
-        <v>644.16</v>
-      </c>
-      <c r="O23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="11" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="Q23" s="11" t="n">
         <v>648.85</v>
       </c>
-      <c r="R23" s="8" t="inlineStr"/>
+      <c r="O23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -6450,18 +5664,9 @@
         <v>0.55</v>
       </c>
       <c r="N24" s="11" t="n">
-        <v>316.8</v>
-      </c>
-      <c r="O24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q24" s="11" t="n">
         <v>319.1</v>
       </c>
-      <c r="R24" s="8" t="inlineStr"/>
+      <c r="O24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -6518,18 +5723,9 @@
         <v>0.28</v>
       </c>
       <c r="N25" s="11" t="n">
-        <v>403.2</v>
-      </c>
-      <c r="O25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="11" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Q25" s="11" t="n">
         <v>406.13</v>
       </c>
-      <c r="R25" s="8" t="inlineStr"/>
+      <c r="O25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -6586,18 +5782,9 @@
         <v>1.08</v>
       </c>
       <c r="N26" s="11" t="n">
-        <v>567</v>
-      </c>
-      <c r="O26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="11" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="Q26" s="11" t="n">
         <v>571.12</v>
       </c>
-      <c r="R26" s="8" t="inlineStr"/>
+      <c r="O26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -6654,18 +5841,9 @@
         <v>0.23</v>
       </c>
       <c r="N27" s="11" t="n">
-        <v>92</v>
-      </c>
-      <c r="O27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="Q27" s="11" t="n">
         <v>92.67</v>
       </c>
-      <c r="R27" s="8" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -6722,18 +5900,9 @@
         <v>0.15</v>
       </c>
       <c r="N28" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="O28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Q28" s="11" t="n">
         <v>151.09</v>
       </c>
-      <c r="R28" s="8" t="inlineStr"/>
+      <c r="O28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -6790,18 +5959,9 @@
         <v>0.98</v>
       </c>
       <c r="N29" s="11" t="n">
-        <v>196</v>
-      </c>
-      <c r="O29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q29" s="11" t="n">
         <v>197.43</v>
       </c>
-      <c r="R29" s="8" t="inlineStr"/>
+      <c r="O29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -6858,18 +6018,9 @@
         <v>0.44</v>
       </c>
       <c r="N30" s="11" t="n">
-        <v>178.2</v>
-      </c>
-      <c r="O30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q30" s="11" t="n">
         <v>179.5</v>
       </c>
-      <c r="R30" s="8" t="inlineStr"/>
+      <c r="O30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -6926,18 +6077,9 @@
         <v>0.35</v>
       </c>
       <c r="N31" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="O31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q31" s="11" t="n">
         <v>211.53</v>
       </c>
-      <c r="R31" s="8" t="inlineStr"/>
+      <c r="O31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -6994,18 +6136,9 @@
         <v>1.1</v>
       </c>
       <c r="N32" s="11" t="n">
-        <v>352</v>
-      </c>
-      <c r="O32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q32" s="11" t="n">
         <v>354.56</v>
       </c>
-      <c r="R32" s="8" t="inlineStr"/>
+      <c r="O32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -7062,18 +6195,9 @@
         <v>1.85</v>
       </c>
       <c r="N33" s="11" t="n">
-        <v>462.5</v>
-      </c>
-      <c r="O33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="11" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Q33" s="11" t="n">
         <v>465.86</v>
       </c>
-      <c r="R33" s="8" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -7130,18 +6254,9 @@
         <v>1.15</v>
       </c>
       <c r="N34" s="11" t="n">
-        <v>230</v>
-      </c>
-      <c r="O34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q34" s="11" t="n">
         <v>231.67</v>
       </c>
-      <c r="R34" s="8" t="inlineStr"/>
+      <c r="O34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -7198,18 +6313,9 @@
         <v>2.88</v>
       </c>
       <c r="N35" s="11" t="n">
-        <v>576</v>
-      </c>
-      <c r="O35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="11" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="Q35" s="11" t="n">
         <v>580.1900000000001</v>
       </c>
-      <c r="R35" s="8" t="inlineStr"/>
+      <c r="O35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -7266,18 +6372,9 @@
         <v>1.46</v>
       </c>
       <c r="N36" s="11" t="n">
-        <v>292</v>
-      </c>
-      <c r="O36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q36" s="11" t="n">
         <v>294.12</v>
       </c>
-      <c r="R36" s="8" t="inlineStr"/>
+      <c r="O36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -7334,18 +6431,9 @@
         <v>1.13</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>1130</v>
-      </c>
-      <c r="O37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="11" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="Q37" s="11" t="n">
         <v>1138.22</v>
       </c>
-      <c r="R37" s="8" t="inlineStr"/>
+      <c r="O37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -7402,18 +6490,9 @@
         <v>0.19</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>114</v>
-      </c>
-      <c r="O38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="11" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Q38" s="11" t="n">
         <v>114.83</v>
       </c>
-      <c r="R38" s="8" t="inlineStr"/>
+      <c r="O38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -7470,18 +6549,9 @@
         <v>0.47</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>282</v>
-      </c>
-      <c r="O39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q39" s="11" t="n">
         <v>284.05</v>
       </c>
-      <c r="R39" s="8" t="inlineStr"/>
+      <c r="O39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -7538,18 +6608,9 @@
         <v>0.18</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>180</v>
-      </c>
-      <c r="O40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Q40" s="11" t="n">
         <v>181.31</v>
       </c>
-      <c r="R40" s="8" t="inlineStr"/>
+      <c r="O40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -7606,18 +6667,9 @@
         <v>0.31</v>
       </c>
       <c r="N41" s="11" t="n">
-        <v>186</v>
-      </c>
-      <c r="O41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Q41" s="11" t="n">
         <v>187.35</v>
       </c>
-      <c r="R41" s="8" t="inlineStr"/>
+      <c r="O41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -7674,18 +6726,9 @@
         <v>1.04</v>
       </c>
       <c r="N42" s="11" t="n">
-        <v>624</v>
-      </c>
-      <c r="O42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="11" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="Q42" s="11" t="n">
         <v>628.54</v>
       </c>
-      <c r="R42" s="8" t="inlineStr"/>
+      <c r="O42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -7742,18 +6785,9 @@
         <v>0.31</v>
       </c>
       <c r="N43" s="11" t="n">
-        <v>155</v>
-      </c>
-      <c r="O43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Q43" s="11" t="n">
         <v>156.13</v>
       </c>
-      <c r="R43" s="8" t="inlineStr"/>
+      <c r="O43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -7810,18 +6844,9 @@
         <v>2.45</v>
       </c>
       <c r="N44" s="11" t="n">
-        <v>612.5</v>
-      </c>
-      <c r="O44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="11" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Q44" s="11" t="n">
         <v>616.95</v>
       </c>
-      <c r="R44" s="8" t="inlineStr"/>
+      <c r="O44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -7878,18 +6903,9 @@
         <v>0.5</v>
       </c>
       <c r="N45" s="11" t="n">
-        <v>125</v>
-      </c>
-      <c r="O45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="11" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="Q45" s="11" t="n">
         <v>125.91</v>
       </c>
-      <c r="R45" s="8" t="inlineStr"/>
+      <c r="O45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -7946,18 +6962,9 @@
         <v>0.52</v>
       </c>
       <c r="N46" s="11" t="n">
-        <v>208</v>
-      </c>
-      <c r="O46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q46" s="11" t="n">
         <v>209.51</v>
       </c>
-      <c r="R46" s="8" t="inlineStr"/>
+      <c r="O46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -8014,18 +7021,9 @@
         <v>0.82</v>
       </c>
       <c r="N47" s="11" t="n">
-        <v>164</v>
-      </c>
-      <c r="O47" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Q47" s="11" t="n">
         <v>165.19</v>
       </c>
-      <c r="R47" s="8" t="inlineStr"/>
+      <c r="O47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -8082,18 +7080,9 @@
         <v>0.16</v>
       </c>
       <c r="N48" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="O48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="11" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="Q48" s="11" t="n">
         <v>80.58</v>
       </c>
-      <c r="R48" s="8" t="inlineStr"/>
+      <c r="O48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -8150,18 +7139,9 @@
         <v>1.05</v>
       </c>
       <c r="N49" s="11" t="n">
-        <v>189</v>
-      </c>
-      <c r="O49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q49" s="11" t="n">
         <v>190.37</v>
       </c>
-      <c r="R49" s="8" t="inlineStr"/>
+      <c r="O49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -8218,18 +7198,9 @@
         <v>0.83</v>
       </c>
       <c r="N50" s="11" t="n">
-        <v>2490</v>
-      </c>
-      <c r="O50" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="11" t="n">
-        <v>18.11</v>
-      </c>
-      <c r="Q50" s="11" t="n">
         <v>2508.11</v>
       </c>
-      <c r="R50" s="8" t="inlineStr"/>
+      <c r="O50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -8286,18 +7257,9 @@
         <v>3.85</v>
       </c>
       <c r="N51" s="11" t="n">
-        <v>1293.6</v>
-      </c>
-      <c r="O51" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="11" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="Q51" s="11" t="n">
         <v>1303.01</v>
       </c>
-      <c r="R51" s="8" t="inlineStr"/>
+      <c r="O51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -8354,18 +7316,9 @@
         <v>0.36</v>
       </c>
       <c r="N52" s="11" t="n">
-        <v>360</v>
-      </c>
-      <c r="O52" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q52" s="11" t="n">
         <v>362.62</v>
       </c>
-      <c r="R52" s="8" t="inlineStr"/>
+      <c r="O52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -8422,18 +7375,9 @@
         <v>0.65</v>
       </c>
       <c r="N53" s="11" t="n">
-        <v>130</v>
-      </c>
-      <c r="O53" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="Q53" s="11" t="n">
         <v>130.95</v>
       </c>
-      <c r="R53" s="8" t="inlineStr"/>
+      <c r="O53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -8490,18 +7434,9 @@
         <v>4.6</v>
       </c>
       <c r="N54" s="11" t="n">
-        <v>1380</v>
-      </c>
-      <c r="O54" s="11" t="n">
-        <v>-100.19</v>
-      </c>
-      <c r="P54" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="11" t="n">
         <v>1279.81</v>
       </c>
-      <c r="R54" s="8" t="inlineStr"/>
+      <c r="O54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -8558,18 +7493,9 @@
         <v>2.62</v>
       </c>
       <c r="N55" s="11" t="n">
-        <v>1650.6</v>
-      </c>
-      <c r="O55" s="11" t="n">
-        <v>-119.83</v>
-      </c>
-      <c r="P55" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="11" t="n">
         <v>1530.77</v>
       </c>
-      <c r="R55" s="8" t="inlineStr"/>
+      <c r="O55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -8626,18 +7552,9 @@
         <v>5.98</v>
       </c>
       <c r="N56" s="11" t="n">
-        <v>430.56</v>
-      </c>
-      <c r="O56" s="11" t="n">
-        <v>-31.26</v>
-      </c>
-      <c r="P56" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="11" t="n">
         <v>399.3</v>
       </c>
-      <c r="R56" s="8" t="inlineStr"/>
+      <c r="O56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -8694,18 +7611,9 @@
         <v>3.55</v>
       </c>
       <c r="N57" s="11" t="n">
-        <v>1278</v>
-      </c>
-      <c r="O57" s="11" t="n">
-        <v>-92.78</v>
-      </c>
-      <c r="P57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="11" t="n">
         <v>1185.22</v>
       </c>
-      <c r="R57" s="8" t="inlineStr"/>
+      <c r="O57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -8762,18 +7670,9 @@
         <v>2.47</v>
       </c>
       <c r="N58" s="11" t="n">
-        <v>829.92</v>
-      </c>
-      <c r="O58" s="11" t="n">
-        <v>-60.25</v>
-      </c>
-      <c r="P58" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="11" t="n">
         <v>769.67</v>
       </c>
-      <c r="R58" s="8" t="inlineStr"/>
+      <c r="O58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -8830,18 +7729,9 @@
         <v>3.99</v>
       </c>
       <c r="N59" s="11" t="n">
-        <v>574.5599999999999</v>
-      </c>
-      <c r="O59" s="11" t="n">
-        <v>-41.71</v>
-      </c>
-      <c r="P59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="11" t="n">
         <v>532.85</v>
       </c>
-      <c r="R59" s="8" t="inlineStr"/>
+      <c r="O59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -8898,18 +7788,9 @@
         <v>1.76</v>
       </c>
       <c r="N60" s="11" t="n">
-        <v>1077.12</v>
-      </c>
-      <c r="O60" s="11" t="n">
-        <v>-78.2</v>
-      </c>
-      <c r="P60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="11" t="n">
         <v>998.92</v>
       </c>
-      <c r="R60" s="8" t="inlineStr"/>
+      <c r="O60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -8966,18 +7847,9 @@
         <v>3.05</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>1537.2</v>
-      </c>
-      <c r="O61" s="11" t="n">
-        <v>-111.6</v>
-      </c>
-      <c r="P61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="11" t="n">
         <v>1425.6</v>
       </c>
-      <c r="R61" s="8" t="inlineStr"/>
+      <c r="O61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -9034,18 +7906,9 @@
         <v>2.08</v>
       </c>
       <c r="N62" s="11" t="n">
-        <v>3494.4</v>
-      </c>
-      <c r="O62" s="11" t="n">
-        <v>-253.7</v>
-      </c>
-      <c r="P62" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="11" t="n">
         <v>3240.7</v>
       </c>
-      <c r="R62" s="8" t="inlineStr"/>
+      <c r="O62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -9102,18 +7965,9 @@
         <v>0.59</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>1298</v>
-      </c>
-      <c r="O63" s="11" t="n">
-        <v>-94.23999999999999</v>
-      </c>
-      <c r="P63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="11" t="n">
         <v>1203.76</v>
       </c>
-      <c r="R63" s="8" t="inlineStr"/>
+      <c r="O63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -9170,18 +8024,9 @@
         <v>0.76</v>
       </c>
       <c r="N64" s="11" t="n">
-        <v>304</v>
-      </c>
-      <c r="O64" s="11" t="n">
-        <v>-33.58</v>
-      </c>
-      <c r="P64" s="11" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="Q64" s="11" t="n">
         <v>279.63</v>
       </c>
-      <c r="R64" s="8" t="inlineStr"/>
+      <c r="O64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -9238,18 +8083,9 @@
         <v>1.45</v>
       </c>
       <c r="N65" s="11" t="n">
-        <v>417.6</v>
-      </c>
-      <c r="O65" s="11" t="n">
-        <v>-46.13</v>
-      </c>
-      <c r="P65" s="11" t="n">
-        <v>12.65</v>
-      </c>
-      <c r="Q65" s="11" t="n">
         <v>384.12</v>
       </c>
-      <c r="R65" s="8" t="inlineStr"/>
+      <c r="O65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -9306,18 +8142,9 @@
         <v>2.75</v>
       </c>
       <c r="N66" s="11" t="n">
-        <v>231</v>
-      </c>
-      <c r="O66" s="11" t="n">
-        <v>-25.52</v>
-      </c>
-      <c r="P66" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q66" s="11" t="n">
         <v>212.48</v>
       </c>
-      <c r="R66" s="8" t="inlineStr"/>
+      <c r="O66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -9374,18 +8201,9 @@
         <v>0.3</v>
       </c>
       <c r="N67" s="11" t="n">
-        <v>240</v>
-      </c>
-      <c r="O67" s="11" t="n">
-        <v>-26.51</v>
-      </c>
-      <c r="P67" s="11" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="Q67" s="11" t="n">
         <v>220.76</v>
       </c>
-      <c r="R67" s="8" t="inlineStr"/>
+      <c r="O67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -9442,18 +8260,9 @@
         <v>0.25</v>
       </c>
       <c r="N68" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="O68" s="11" t="n">
-        <v>-27.62</v>
-      </c>
-      <c r="P68" s="11" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="Q68" s="11" t="n">
         <v>229.95</v>
       </c>
-      <c r="R68" s="8" t="inlineStr"/>
+      <c r="O68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -9510,18 +8319,9 @@
         <v>1.25</v>
       </c>
       <c r="N69" s="11" t="n">
-        <v>625</v>
-      </c>
-      <c r="O69" s="11" t="n">
-        <v>-69.04000000000001</v>
-      </c>
-      <c r="P69" s="11" t="n">
-        <v>18.93</v>
-      </c>
-      <c r="Q69" s="11" t="n">
         <v>574.89</v>
       </c>
-      <c r="R69" s="8" t="inlineStr"/>
+      <c r="O69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -9578,18 +8378,9 @@
         <v>3.5</v>
       </c>
       <c r="N70" s="11" t="n">
-        <v>2205</v>
-      </c>
-      <c r="O70" s="11" t="n">
-        <v>-243.57</v>
-      </c>
-      <c r="P70" s="11" t="n">
-        <v>66.78</v>
-      </c>
-      <c r="Q70" s="11" t="n">
         <v>2028.21</v>
       </c>
-      <c r="R70" s="8" t="inlineStr"/>
+      <c r="O70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -9646,18 +8437,9 @@
         <v>0.86</v>
       </c>
       <c r="N71" s="11" t="n">
-        <v>258</v>
-      </c>
-      <c r="O71" s="11" t="n">
-        <v>-28.5</v>
-      </c>
-      <c r="P71" s="11" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="Q71" s="11" t="n">
         <v>237.32</v>
       </c>
-      <c r="R71" s="8" t="inlineStr"/>
+      <c r="O71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -9714,18 +8496,9 @@
         <v>0.32</v>
       </c>
       <c r="N72" s="11" t="n">
-        <v>96</v>
-      </c>
-      <c r="O72" s="11" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="P72" s="11" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Q72" s="11" t="n">
         <v>88.31</v>
       </c>
-      <c r="R72" s="8" t="inlineStr"/>
+      <c r="O72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -9782,21 +8555,12 @@
         <v>1.52</v>
       </c>
       <c r="N73" s="11" t="n">
-        <v>1976</v>
-      </c>
-      <c r="O73" s="11" t="n">
-        <v>-218.28</v>
-      </c>
-      <c r="P73" s="11" t="n">
-        <v>59.86</v>
-      </c>
-      <c r="Q73" s="11" t="n">
         <v>1817.58</v>
       </c>
-      <c r="R73" s="8" t="inlineStr"/>
+      <c r="O73" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R73"/>
+  <autoFilter ref="A1:O73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9807,7 +8571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10309,7 +9073,7 @@
     <row r="44">
       <c r="A44" s="32" t="inlineStr">
         <is>
-          <t>SLEVY A ROZPUSTENI DO CELNI HODNOTY</t>
+          <t>CENA - BERE SE CASTKA UVEDENA U "TOTAL"</t>
         </is>
       </c>
       <c r="B44" s="33" t="n"/>
@@ -10317,156 +9081,203 @@
     <row r="45">
       <c r="A45" s="34" t="inlineStr">
         <is>
-          <t>Ningbo Onway Imp &amp; Exp Co., Ltd.</t>
+          <t>Pravidlo</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Zadna sleva nebyla na fakture uplatnena.</t>
+          <t>Jako cena / celni hodnota se bere castka uvedena na dokladu u "Total" - jedna jedina castka, nikoli castka pred slevou a po sleve zvlast.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="34" t="inlineStr">
         <is>
+          <t>Castky u "Total"</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Ningbo Onway, fa 26OW08001 LCL14 ... "TOTAL US$40,162.42"
+Hefei Howell, fa 4L26016S/1 ....... "USD Total $12,566.60"
+Ningbo HowellGoods, fa 4L26016S/2 . "USD Total $6,073.25"
+SOUCET ............................ 58 802,27 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t>Rozpad na HS kody</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Castka u "Total" je za celou fakturu, proto je na jednotlive HS kody rozpocitana pomerne podle hodnoty radku. Soucet radku u kazdeho odesilatele se rovna presne castce u "Total" na jeho fakture. V souhrnu je proto jen jeden cenovy sloupec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>JAK VZNIKLA CASTKA U "TOTAL" (jen pro informaci)</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>Ningbo Onway Imp &amp; Exp Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Zadna sleva nebyla na fakture uplatnena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
           <t>Hefei Howell E-commerce Co., Ltd.</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Sleva celkem -983.76 USD z ceny zbozi 13550.36 USD (7.2600 %), rozpustena pomerne podle hodnoty na jednotlive HS kody.
 Slozky: Sleva - devalvace jüanu 7,26 % = -983.76 USD</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="34" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t>Ningbo HowellGoods Import and Export Co., Ltd.</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Sleva celkem -729.35 USD z ceny zbozi 6602.60 USD (11.0464 %), rozpustena pomerne podle hodnoty na jednotlive HS kody.
 Slozky: Sleva - devalvace jüanu 7,26 % = -479.35 USD; Sleva za kontejner = -250.00 USD</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="35" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>Naklady LCL</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>Ningbo Onway "Extra cost for the LCL" +290,00 USD a Ningbo HowellGoods "LCL cost for LCL14" +200,00 USD jsou naklady na prepravu uctovane prodavajicim na fakture. Podle cl. 71 odst. 1 pism. e) celniho kodexu Unie se naklady na prepravu az na misto vstupu do celniho uzemi EU PRIPOCITAVAJI k celni hodnote - jsou proto pomerne rozpusteny podle hodnoty do jednotlivych HS kodu (samostatny sloupec "Naklady LCL").</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="35" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>Celni hodnota - upozorneni</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>Uvedena celni hodnota (58 802,27 USD) odpovida souctu vsech tri faktur, tj. cena FOB Ningbo po slevach + LCL naklady uctovane prodavajicimi. Dodaci podminka je FOB, proto je pro konecne celni prohlaseni nutne k teto hodnote jeste PRIPOCIST namorni prepravne a pojisteni az na misto vstupu do EU podle fakturace speditera - tyto castky nejsou v predanych dokladech obsazeny.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="32" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t>KONTROLA PROTI DOKLADUM</t>
         </is>
       </c>
-      <c r="B50" s="33" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="34" t="inlineStr">
-        <is>
-          <t>Ningbo Onway Imp &amp; Exp Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Ks 31277 | cista hm. 6753.300 kg | hruba hm. 7219.200 kg | cena zbozi 39872.42 USD | sleva 0.00 USD | naklady LCL 290.00 USD | celni hodnota 40162.42 USD (= celkem dle faktury 40162.42 USD) | pocet unikatnich HS kodu 37
-Kazda radka faktury i balicino listu byla znovu nactena primo z PDF a porovnana: mnozstvi, jednotkove ceny, castky, kartony i hmotnosti souhlasi bez rozdilu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="34" t="inlineStr">
-        <is>
-          <t>Hefei Howell E-commerce Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Ks 6838 | cista hm. 2553.300 kg | hruba hm. 2714.300 kg | cena zbozi 13550.36 USD | sleva -983.76 USD | naklady LCL 0.00 USD | celni hodnota 12566.60 USD (= celkem dle faktury 12566.60 USD) | pocet unikatnich HS kodu 9
-Kazda radka faktury i balicino listu byla znovu nactena primo z PDF a porovnana: mnozstvi, jednotkove ceny, castky, kartony i hmotnosti souhlasi bez rozdilu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="34" t="inlineStr">
-        <is>
-          <t>Ningbo HowellGoods Import and Export Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Ks 5602 | cista hm. 859.600 kg | hruba hm. 924.600 kg | cena zbozi 6602.60 USD | sleva -729.35 USD | naklady LCL 200.00 USD | celni hodnota 6073.25 USD (= celkem dle faktury 6073.25 USD) | pocet unikatnich HS kodu 9
-Kazda radka faktury i balicino listu byla znovu nactena primo z PDF a porovnana: mnozstvi, jednotkove ceny, castky, kartony i hmotnosti souhlasi bez rozdilu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="34" t="inlineStr">
-        <is>
-          <t>CELKEM</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Ks 43717 | cista hm. 10166.200 kg | hruba hm. 10858.100 kg | cena zbozi 60025.38 USD | sleva -1713.11 USD | naklady LCL 490.00 USD | CELNI HODNOTA 58802.27 USD | 72 polozek -&gt; 55 radku souhrnu
-Souhlasi se souctem fakturovanych castek: 40 162,42 + 12 566,60 + 6 073,25 = 58 802,27 USD.</t>
-        </is>
-      </c>
+      <c r="B54" s="33" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="34" t="inlineStr">
         <is>
-          <t>Uplnost HS kodu</t>
+          <t>Ningbo Onway Imp &amp; Exp Co., Ltd.</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Vsech 72 polozek melo HS kod i cesky popis primo v podkladech klienta (Popis_2026LCL14.xlsx). Pravidlo CCT/VPV KN tarifni zarazeni nebylo nutne pouzit - zadny kod nebyl odvozovan.</t>
+          <t>Ks 31277 | cista hm. 6753.300 kg | hruba hm. 7219.200 kg | cena 40162.42 USD (= castka u "Total" na fakture 40162.42 USD) | pocet unikatnich HS kodu 37
+Kazda radka faktury i balicino listu byla znovu nactena primo z PDF a porovnana: mnozstvi, jednotkove ceny, castky, kartony i hmotnosti souhlasi bez rozdilu.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>Popisy</t>
+          <t>Hefei Howell E-commerce Co., Ltd.</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Sloupec "Popis" obsahuje doslovne cesky nazev z podkladu klienta (sloupec "CZ name"), bez jakekoli upravy. Vedle nej je nove i sloupec "Celni popis" - rovnez doslovny cesky text klienta ze sloupce "Celni popis". Zadny popis nebyl prekladan ani prepisovan. U radku, kde se do jednoho HS kodu slucuje vic polozek, jsou popisy spojeny strednikem, aby se zadny neztratil.</t>
+          <t>Ks 6838 | cista hm. 2553.300 kg | hruba hm. 2714.300 kg | cena 12566.60 USD (= castka u "Total" na fakture 12566.60 USD) | pocet unikatnich HS kodu 9
+Kazda radka faktury i balicino listu byla znovu nactena primo z PDF a porovnana: mnozstvi, jednotkove ceny, castky, kartony i hmotnosti souhlasi bez rozdilu.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="34" t="inlineStr">
         <is>
+          <t>Ningbo HowellGoods Import and Export Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Ks 5602 | cista hm. 859.600 kg | hruba hm. 924.600 kg | cena 6073.25 USD (= castka u "Total" na fakture 6073.25 USD) | pocet unikatnich HS kodu 9
+Kazda radka faktury i balicino listu byla znovu nactena primo z PDF a porovnana: mnozstvi, jednotkove ceny, castky, kartony i hmotnosti souhlasi bez rozdilu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>CELKEM</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Ks 43717 | cista hm. 10166.200 kg | hruba hm. 10858.100 kg | CENA 58802.27 USD | 72 polozek -&gt; 55 radku souhrnu
+Souhlasi se souctem castek u "Total": 40 162,42 + 12 566,60 + 6 073,25 = 58 802,27 USD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t>Uplnost HS kodu</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Vsech 72 polozek melo HS kod i cesky popis primo v podkladech klienta (Popis_2026LCL14.xlsx). Pravidlo CCT/VPV KN tarifni zarazeni nebylo nutne pouzit - zadny kod nebyl odvozovan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t>Popisy</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Sloupec "Popis" obsahuje doslovne cesky nazev z podkladu klienta (sloupec "CZ name"), bez jakekoli upravy. Vedle nej je nove i sloupec "Celni popis" - rovnez doslovny cesky text klienta ze sloupce "Celni popis". Zadny popis nebyl prekladan ani prepisovan. U radku, kde se do jednoho HS kodu slucuje vic polozek, jsou popisy spojeny strednikem, aby se zadny neztratil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
           <t>Hmotnosti - zdroj</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Cista i hruba hmotnost pochazi vyhradne z balicich listu. Souhrnne hodnoty: cista 10 166,200 kg, hruba 10 858,100 kg - soucet odpovida souctum uvedenym primo v balicich listech (6 753,300 + 2 553,300 + 859,600 a 7 219,200 + 2 714,300 + 924,600). Nejde o hmotnost kontejneru vcetne palet, nybrz o hmotnost zbozi vcetne obalu dle PL.</t>
         </is>
